--- a/Data/TestDataPoland-Regression.xlsx
+++ b/Data/TestDataPoland-Regression.xlsx
@@ -259,7 +259,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699016</t>
+    <t>10699062</t>
   </si>
   <si>
     <t>Passed</t>
@@ -271,10 +271,10 @@
     <t>Poland</t>
   </si>
   <si>
-    <t>Riley</t>
-  </si>
-  <si>
-    <t>Lockman</t>
+    <t>Daryl</t>
+  </si>
+  <si>
+    <t>Tremblay</t>
   </si>
   <si>
     <t xml:space="preserve">698 980 460 </t>
@@ -373,7 +373,7 @@
     <t>ID Card</t>
   </si>
   <si>
-    <t>SSK456130</t>
+    <t>SSK456150</t>
   </si>
   <si>
     <t>Male</t>
@@ -415,19 +415,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699018</t>
+    <t>10699063</t>
   </si>
   <si>
     <t>765 Store Management (Kires Pivyba (10226524))</t>
   </si>
   <si>
-    <t>Theron</t>
-  </si>
-  <si>
-    <t>Conn-Hoeger</t>
-  </si>
-  <si>
-    <t>Auto 81040702</t>
+    <t>Laverna</t>
+  </si>
+  <si>
+    <t>Sauer</t>
+  </si>
+  <si>
+    <t>Auto 58547236</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>SSK456131</t>
+    <t>SSK456151</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1551,7 @@
         <v>111</v>
       </c>
       <c r="BF2" s="15">
-        <v>9477796619</v>
+        <v>9477796660</v>
       </c>
       <c r="BG2" s="36" t="s">
         <v>79</v>
@@ -1560,7 +1560,7 @@
         <v>112</v>
       </c>
       <c r="BI2" s="15">
-        <v>49678965351</v>
+        <v>49678965370</v>
       </c>
       <c r="BJ2" s="36" t="s">
         <v>79</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K3" s="37">
         <f t="shared" ref="K3" si="0">TODAY()-31</f>
-        <v>45755</v>
+        <v>45761</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>79</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="X3" s="38">
         <f t="shared" ref="X3" si="1">K3</f>
-        <v>45755</v>
+        <v>45761</v>
       </c>
       <c r="Y3" s="36" t="s">
         <v>92</v>
@@ -1790,7 +1790,7 @@
         <v>111</v>
       </c>
       <c r="BF3" s="15">
-        <v>9477796620</v>
+        <v>9477796661</v>
       </c>
       <c r="BG3" s="36" t="s">
         <v>79</v>
@@ -1799,7 +1799,7 @@
         <v>112</v>
       </c>
       <c r="BI3" s="15">
-        <v>49678965352</v>
+        <v>49678965371</v>
       </c>
       <c r="BJ3" s="36" t="s">
         <v>79</v>

--- a/Data/TestDataPoland-Regression.xlsx
+++ b/Data/TestDataPoland-Regression.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
@@ -259,7 +259,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699062</t>
+    <t>10699098</t>
   </si>
   <si>
     <t>Passed</t>
@@ -271,10 +271,10 @@
     <t>Poland</t>
   </si>
   <si>
-    <t>Daryl</t>
-  </si>
-  <si>
-    <t>Tremblay</t>
+    <t>Kayla</t>
+  </si>
+  <si>
+    <t>Koelpin</t>
   </si>
   <si>
     <t xml:space="preserve">698 980 460 </t>
@@ -373,7 +373,7 @@
     <t>ID Card</t>
   </si>
   <si>
-    <t>SSK456150</t>
+    <t>SSK456152</t>
   </si>
   <si>
     <t>Male</t>
@@ -415,19 +415,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699063</t>
+    <t>10699099</t>
   </si>
   <si>
     <t>765 Store Management (Kires Pivyba (10226524))</t>
   </si>
   <si>
-    <t>Laverna</t>
-  </si>
-  <si>
-    <t>Sauer</t>
-  </si>
-  <si>
-    <t>Auto 58547236</t>
+    <t>Blaise</t>
+  </si>
+  <si>
+    <t>Mann</t>
+  </si>
+  <si>
+    <t>Auto 97391177</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>SSK456151</t>
+    <t>SSK456153</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1551,7 @@
         <v>111</v>
       </c>
       <c r="BF2" s="15">
-        <v>9477796660</v>
+        <v>9577796660</v>
       </c>
       <c r="BG2" s="36" t="s">
         <v>79</v>
@@ -1560,7 +1560,7 @@
         <v>112</v>
       </c>
       <c r="BI2" s="15">
-        <v>49678965370</v>
+        <v>49778965370</v>
       </c>
       <c r="BJ2" s="36" t="s">
         <v>79</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K3" s="37">
         <f t="shared" ref="K3" si="0">TODAY()-31</f>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>79</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="X3" s="38">
         <f t="shared" ref="X3" si="1">K3</f>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="Y3" s="36" t="s">
         <v>92</v>
@@ -1790,7 +1790,7 @@
         <v>111</v>
       </c>
       <c r="BF3" s="15">
-        <v>9477796661</v>
+        <v>9577796661</v>
       </c>
       <c r="BG3" s="36" t="s">
         <v>79</v>
@@ -1799,7 +1799,7 @@
         <v>112</v>
       </c>
       <c r="BI3" s="15">
-        <v>49678965371</v>
+        <v>49778965371</v>
       </c>
       <c r="BJ3" s="36" t="s">
         <v>79</v>
